--- a/graph_data.xlsx
+++ b/graph_data.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repositories\Sensor-Placement-Optimization-in-Water-Systems\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repositories\Sensor-Placement-Optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E4AE91-9A2D-4E5E-A5D1-EDC932904374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9E7ACE-EC95-40B8-A890-34A9E2179AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="8844" windowHeight="12360" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dummy_graph_nodes" sheetId="1" r:id="rId1"/>
     <sheet name="dummy_graph_edges" sheetId="4" r:id="rId2"/>
     <sheet name="test_network1_nodes" sheetId="2" r:id="rId3"/>
     <sheet name="test_network1_edges" sheetId="5" r:id="rId4"/>
-    <sheet name="test_network2" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="10">
   <si>
     <t>source</t>
   </si>
@@ -56,6 +55,9 @@
   </si>
   <si>
     <t>node_id</t>
+  </si>
+  <si>
+    <t>weight</t>
   </si>
 </sst>
 </file>
@@ -577,7 +579,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4F1AA4-5B06-4E0E-91BF-56C15A6BC0BE}">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -596,7 +598,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -605,12 +607,12 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
@@ -619,12 +621,12 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>0</v>
@@ -633,12 +635,12 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -647,12 +649,12 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>0</v>
@@ -661,12 +663,12 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -675,12 +677,12 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>0</v>
@@ -689,12 +691,12 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>2</v>
@@ -703,82 +705,82 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="D11">
         <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>8</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>0</v>
@@ -792,21 +794,21 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -815,74 +817,74 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="C18">
+        <v>9</v>
+      </c>
+      <c r="D18">
         <v>10</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -890,7 +892,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
@@ -899,18 +901,18 @@
         <v>12</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -918,35 +920,35 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -955,71 +957,71 @@
         <v>14</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>16</v>
@@ -1030,35 +1032,35 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>16</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -1067,110 +1069,110 @@
         <v>18</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C39">
         <v>20</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41">
         <v>22</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>2</v>
@@ -1179,54 +1181,54 @@
         <v>24</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>2</v>
@@ -1235,18 +1237,18 @@
         <v>26</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1254,41 +1256,41 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>0</v>
       </c>
       <c r="C51">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1296,77 +1298,77 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C52">
         <v>28</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C53">
         <v>28</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>30</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
@@ -1375,26 +1377,26 @@
         <v>32</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
         <v>2</v>
@@ -1403,82 +1405,82 @@
         <v>34</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C63">
         <v>36</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>2</v>
@@ -1487,82 +1489,82 @@
         <v>38</v>
       </c>
       <c r="D65">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C69">
         <v>40</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
@@ -1571,68 +1573,68 @@
         <v>42</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D75">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
@@ -1641,60 +1643,60 @@
         <v>43</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D78">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D79">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80">
         <v>6</v>
@@ -1702,203 +1704,203 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C81">
         <v>44</v>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C83">
         <v>46</v>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D84">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C85">
         <v>48</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>50</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C89">
         <v>52</v>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C91">
         <v>54</v>
       </c>
       <c r="D91">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C93">
         <v>56</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
         <v>2</v>
@@ -1907,119 +1909,105 @@
         <v>58</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C99">
         <v>60</v>
       </c>
       <c r="D99">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C101">
         <v>62</v>
       </c>
       <c r="D101">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D102">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="s">
-        <v>1</v>
-      </c>
-      <c r="C103">
-        <v>64</v>
-      </c>
-      <c r="D103">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2046,835 +2034,1121 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EADE6ED2-07FC-448B-AA29-D284AD2D0ED9}">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>14</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>21</v>
+      </c>
+      <c r="C23">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>27</v>
+      </c>
+      <c r="C26">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>29</v>
+      </c>
+      <c r="B27">
+        <v>27</v>
+      </c>
+      <c r="C27">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>25</v>
+      </c>
+      <c r="C29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>25</v>
+      </c>
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>24</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>32</v>
+      </c>
+      <c r="C32">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>33</v>
+      </c>
+      <c r="C35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>32</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>36</v>
+      </c>
+      <c r="C38">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>38</v>
+      </c>
+      <c r="C40">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>41</v>
+      </c>
+      <c r="C43">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>40</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>40</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>46</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>48</v>
+      </c>
+      <c r="B47">
+        <v>47</v>
+      </c>
+      <c r="C47">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>49</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>45</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>45</v>
+      </c>
+      <c r="B50">
+        <v>44</v>
+      </c>
+      <c r="C50">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>44</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>50</v>
+      </c>
+      <c r="C52">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>52</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>52</v>
+      </c>
+      <c r="C54">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>54</v>
+      </c>
+      <c r="C55">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>54</v>
+      </c>
+      <c r="C56">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>56</v>
+      </c>
+      <c r="C57">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>58</v>
+      </c>
+      <c r="B58">
+        <v>57</v>
+      </c>
+      <c r="C58">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>59</v>
+      </c>
+      <c r="B59">
+        <v>57</v>
+      </c>
+      <c r="C59">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>56</v>
+      </c>
+      <c r="C60">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>56</v>
+      </c>
+      <c r="B61">
+        <v>60</v>
+      </c>
+      <c r="C61">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>60</v>
+      </c>
+      <c r="C62">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>62</v>
+      </c>
+      <c r="C63">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>64</v>
+      </c>
+      <c r="B64">
+        <v>63</v>
+      </c>
+      <c r="C64">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>65</v>
+      </c>
+      <c r="B65">
+        <v>63</v>
+      </c>
+      <c r="C65">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66">
+        <v>62</v>
+      </c>
+      <c r="C66">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>62</v>
+      </c>
+      <c r="B67">
+        <v>66</v>
+      </c>
+      <c r="C67">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>66</v>
+      </c>
+      <c r="C68">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69">
+        <v>68</v>
+      </c>
+      <c r="C69">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>71</v>
+      </c>
+      <c r="B70">
+        <v>70</v>
+      </c>
+      <c r="C70">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>72</v>
+      </c>
+      <c r="B71">
+        <v>70</v>
+      </c>
+      <c r="C71">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>69</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>75</v>
+      </c>
+      <c r="B73">
+        <v>74</v>
+      </c>
+      <c r="C73">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>76</v>
+      </c>
+      <c r="B74">
+        <v>74</v>
+      </c>
+      <c r="C74">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>73</v>
+      </c>
+      <c r="C75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>77</v>
+      </c>
+      <c r="B76">
+        <v>73</v>
+      </c>
+      <c r="C76">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>73</v>
+      </c>
+      <c r="B77">
+        <v>69</v>
+      </c>
+      <c r="C77">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>69</v>
+      </c>
+      <c r="B78">
+        <v>68</v>
+      </c>
+      <c r="C78">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>68</v>
+      </c>
+      <c r="B79">
+        <v>78</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>78</v>
+      </c>
+      <c r="C80">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>78</v>
+      </c>
+      <c r="B81">
+        <v>80</v>
+      </c>
+      <c r="C81">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>80</v>
+      </c>
+      <c r="C82">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>80</v>
+      </c>
+      <c r="B83">
+        <v>82</v>
+      </c>
+      <c r="C83">
         <v>13</v>
       </c>
-      <c r="B6">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>82</v>
+      </c>
+      <c r="C84">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>82</v>
+      </c>
+      <c r="B85">
+        <v>84</v>
+      </c>
+      <c r="C85">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>84</v>
+      </c>
+      <c r="C86">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>86</v>
+      </c>
+      <c r="C87">
         <v>16</v>
       </c>
-      <c r="B7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>26</v>
-      </c>
-      <c r="B9">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>32</v>
-      </c>
-      <c r="B10">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>34</v>
-      </c>
-      <c r="B11">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>38</v>
-      </c>
-      <c r="B12">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>86</v>
+      </c>
+      <c r="C88">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>86</v>
+      </c>
+      <c r="B89">
+        <v>88</v>
+      </c>
+      <c r="C89">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>88</v>
+      </c>
+      <c r="C90">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>88</v>
+      </c>
+      <c r="B91">
+        <v>90</v>
+      </c>
+      <c r="C91">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>90</v>
+      </c>
+      <c r="C92">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>90</v>
+      </c>
+      <c r="B93">
+        <v>92</v>
+      </c>
+      <c r="C93">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>94</v>
+      </c>
+      <c r="B94">
+        <v>93</v>
+      </c>
+      <c r="C94">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>40</v>
-      </c>
-      <c r="B13">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>42</v>
-      </c>
-      <c r="B14">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>46</v>
-      </c>
-      <c r="B15">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>52</v>
-      </c>
-      <c r="B16">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>54</v>
-      </c>
-      <c r="B17">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>56</v>
-      </c>
-      <c r="B18">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>58</v>
-      </c>
-      <c r="B19">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>62</v>
-      </c>
-      <c r="B20">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>64</v>
-      </c>
-      <c r="B21">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>68</v>
-      </c>
-      <c r="B22">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>70</v>
-      </c>
-      <c r="B23">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>95</v>
+      </c>
+      <c r="B95">
+        <v>93</v>
+      </c>
+      <c r="C95">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>93</v>
+      </c>
+      <c r="B96">
+        <v>92</v>
+      </c>
+      <c r="C96">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>92</v>
+      </c>
+      <c r="B97">
+        <v>96</v>
+      </c>
+      <c r="C97">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>96</v>
+      </c>
+      <c r="C98">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>80</v>
-      </c>
-      <c r="B24">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>82</v>
-      </c>
-      <c r="B25">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>84</v>
-      </c>
-      <c r="B26">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>86</v>
-      </c>
-      <c r="B27">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>88</v>
-      </c>
-      <c r="B28">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>90</v>
-      </c>
-      <c r="B29">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>92</v>
-      </c>
-      <c r="B30">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>94</v>
-      </c>
-      <c r="B31">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>96</v>
+      </c>
+      <c r="B99">
         <v>98</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="C99">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
         <v>98</v>
       </c>
-      <c r="B32">
+      <c r="C100">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>98</v>
+      </c>
+      <c r="B101">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>100</v>
-      </c>
-      <c r="B33">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>2</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>3</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="C101">
         <v>5</v>
-      </c>
-      <c r="B36">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>7</v>
-      </c>
-      <c r="B37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>9</v>
-      </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>11</v>
-      </c>
-      <c r="B39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>12</v>
-      </c>
-      <c r="B40">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>10</v>
-      </c>
-      <c r="B41">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>14</v>
-      </c>
-      <c r="B42">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>15</v>
-      </c>
-      <c r="B43">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>20</v>
-      </c>
-      <c r="B44">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>21</v>
-      </c>
-      <c r="B45">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>18</v>
-      </c>
-      <c r="B46">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>19</v>
-      </c>
-      <c r="B47">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>17</v>
-      </c>
-      <c r="B48">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>24</v>
-      </c>
-      <c r="B49">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>25</v>
-      </c>
-      <c r="B50">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>23</v>
-      </c>
-      <c r="B51">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>30</v>
-      </c>
-      <c r="B52">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>31</v>
-      </c>
-      <c r="B53">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>29</v>
-      </c>
-      <c r="B54">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>28</v>
-      </c>
-      <c r="B55">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>27</v>
-      </c>
-      <c r="B56">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>33</v>
-      </c>
-      <c r="B57">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>36</v>
-      </c>
-      <c r="B58">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>37</v>
-      </c>
-      <c r="B59">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>35</v>
-      </c>
-      <c r="B60">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>39</v>
-      </c>
-      <c r="B61">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>41</v>
-      </c>
-      <c r="B62">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>44</v>
-      </c>
-      <c r="B63">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>45</v>
-      </c>
-      <c r="B64">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>43</v>
-      </c>
-      <c r="B65">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>50</v>
-      </c>
-      <c r="B66">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>51</v>
-      </c>
-      <c r="B67">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>48</v>
-      </c>
-      <c r="B68">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>49</v>
-      </c>
-      <c r="B69">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>47</v>
-      </c>
-      <c r="B70">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>53</v>
-      </c>
-      <c r="B71">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>55</v>
-      </c>
-      <c r="B72">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>57</v>
-      </c>
-      <c r="B73">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>60</v>
-      </c>
-      <c r="B74">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>61</v>
-      </c>
-      <c r="B75">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>59</v>
-      </c>
-      <c r="B76">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>63</v>
-      </c>
-      <c r="B77">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>66</v>
-      </c>
-      <c r="B78">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>67</v>
-      </c>
-      <c r="B79">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>65</v>
-      </c>
-      <c r="B80">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>69</v>
-      </c>
-      <c r="B81">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>77</v>
-      </c>
-      <c r="B82">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>78</v>
-      </c>
-      <c r="B83">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>76</v>
-      </c>
-      <c r="B84">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>79</v>
-      </c>
-      <c r="B85">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>75</v>
-      </c>
-      <c r="B86">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>71</v>
-      </c>
-      <c r="B87">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>73</v>
-      </c>
-      <c r="B88">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>74</v>
-      </c>
-      <c r="B89">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>72</v>
-      </c>
-      <c r="B90">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>81</v>
-      </c>
-      <c r="B91">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>83</v>
-      </c>
-      <c r="B92">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>85</v>
-      </c>
-      <c r="B93">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>87</v>
-      </c>
-      <c r="B94">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>89</v>
-      </c>
-      <c r="B95">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>91</v>
-      </c>
-      <c r="B96">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>93</v>
-      </c>
-      <c r="B97">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>96</v>
-      </c>
-      <c r="B98">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>97</v>
-      </c>
-      <c r="B99">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>95</v>
-      </c>
-      <c r="B100">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>99</v>
-      </c>
-      <c r="B101">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D77D15BA-638F-49A4-B991-51E68E5051DA}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/graph_data.xlsx
+++ b/graph_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Repositories\Sensor-Placement-Optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9E7ACE-EC95-40B8-A890-34A9E2179AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86A1E20-CC77-4CCA-BC70-B01E0EB60A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8844" windowHeight="12360" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3564" windowWidth="12960" windowHeight="7176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dummy_graph_nodes" sheetId="1" r:id="rId1"/>
